--- a/docs/VAL_CoPilot_Python_Procedures_Catalog.xlsx
+++ b/docs/VAL_CoPilot_Python_Procedures_Catalog.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procedures Catalog" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scripts Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Procedures Catalog'!$A$1:$E$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Procedures Catalog'!$A$1:$E$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Scripts Summary'!$A$1:$F$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,7 +40,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +50,41 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="000B1F33"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9F3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDE9FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -77,14 +114,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -450,17 +509,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="72" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
@@ -493,22 +552,22 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>server.py (mcp.run)</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Entry point</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>FastMCP stdio server; installs LinkSquares offline interceptor when USE_OFFLINE_MOCKS is set and registers all MCP tools</t>
         </is>
@@ -520,24 +579,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>get_expiring_contracts</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Returns contracts approaching expiration within a days_ahead window</t>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Returns contracts approaching expiration within a days_ahead lookahead window</t>
         </is>
       </c>
     </row>
@@ -547,24 +606,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>get_vendor_spend_summary</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>get_contract_renewals</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Rolls up committed contract value by supplier (not invoice spend)</t>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Renewal Window List — contracts coming up for renewal in days_ahead or inclusive window_start/window_end</t>
         </is>
       </c>
     </row>
@@ -574,24 +633,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>compare_contracts</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>get_vendor_spend_summary</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Pairwise or N-way compare of any contract IDs; hard-stops with exact unavailable message if sides cannot be resolved</t>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Rolls up committed contract value by supplier (not invoice spend)</t>
         </is>
       </c>
     </row>
@@ -601,24 +660,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>check_missing_contract_fields</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>compare_contracts</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Scans contracts for incomplete commercial fields</t>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Pairwise or N-way compare of any contract IDs; hard-stops with exact unavailable message if sides cannot be resolved</t>
         </is>
       </c>
     </row>
@@ -628,24 +687,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>search_cloud_blob_contracts</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>check_missing_contract_fields</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Hybrid semantic / clause search via Azure AI Search (or offline search docs)</t>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Scans contracts for incomplete commercial fields</t>
         </is>
       </c>
     </row>
@@ -655,24 +714,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>search_contracts</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>search_cloud_blob_contracts</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Structured Gold metadata search; returns contract_not_present when nothing matches</t>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Hybrid semantic / clause search via Azure AI Search (or offline search docs)</t>
         </is>
       </c>
     </row>
@@ -682,24 +741,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>get_contract_profile</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>search_contracts</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Full normalized profile for one ContractID; not-present if missing</t>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Structured Gold metadata search; returns contract_not_present when nothing matches</t>
         </is>
       </c>
     </row>
@@ -709,24 +768,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>find_overlaps</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>get_contract_profile</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Detects same-vendor effective-to-expiration date overlaps</t>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Full normalized profile for one ContractID; not-present if missing</t>
         </is>
       </c>
     </row>
@@ -736,24 +795,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>explain_contract_risk</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>find_overlaps</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Returns known_facts versus computed_risks for filtered contracts</t>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Detects same-vendor effective-to-expiration date overlaps</t>
         </is>
       </c>
     </row>
@@ -763,24 +822,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>fabric_health_check</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>explain_contract_risk</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Probes Fabric SQL connectivity or offline interceptor health</t>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Returns known_facts versus computed_risks for filtered contracts</t>
         </is>
       </c>
     </row>
@@ -790,24 +849,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>_install_offline_mock_interceptor</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>fabric_health_check</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Patches pyodbc/pandas/Azure Search so production-shaped tools hit LinkSquares fixtures</t>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>MCP Tool</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Probes Fabric SQL connectivity or offline interceptor health</t>
         </is>
       </c>
     </row>
@@ -817,24 +876,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>build_criteria</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>mcp_server/contract_analytics.py</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Builds filter criteria (supplier type id name cost) for resolve/filter paths</t>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>_install_offline_mock_interceptor</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/server.py</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Patches pyodbc/pandas/Azure Search so production-shaped tools hit LinkSquares fixtures</t>
         </is>
       </c>
     </row>
@@ -844,24 +903,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>filter_contracts</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>build_criteria</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
         <is>
           <t>mcp_server/contract_analytics.py</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Filters in-memory contract rows against active criteria</t>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Builds filter criteria (supplier type id name cost) for resolve/filter paths</t>
         </is>
       </c>
     </row>
@@ -871,24 +930,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>resolve_contract</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>filter_contracts</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>mcp_server/contract_analytics.py</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Resolves a single best-matching contract for profile/compare sides</t>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Filters in-memory contract rows against active criteria</t>
         </is>
       </c>
     </row>
@@ -898,24 +957,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>compare_contract_rows</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>resolve_contract</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>mcp_server/contract_analytics.py</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Pairwise field-diff comparison between two resolved contracts</t>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Resolves a single best-matching contract for profile/compare sides</t>
         </is>
       </c>
     </row>
@@ -925,24 +984,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>compare_many_contract_rows</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>compare_contract_rows</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>mcp_server/contract_analytics.py</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>N-way field matrix comparison across any number of resolved contracts</t>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Pairwise field-diff comparison between two resolved contracts</t>
         </is>
       </c>
     </row>
@@ -952,24 +1011,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>check_missing_fields_in_rows</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>compare_many_contract_rows</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
         <is>
           <t>mcp_server/contract_analytics.py</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Computes which required commercial fields are missing on each row</t>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>N-way field matrix comparison across any number of resolved contracts</t>
         </is>
       </c>
     </row>
@@ -979,24 +1038,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>normalize_contract_search_row</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>check_missing_fields_in_rows</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>mcp_server/contract_analytics.py</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Shapes a Gold row into the search_contracts result schema</t>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Computes which required commercial fields are missing on each row</t>
         </is>
       </c>
     </row>
@@ -1006,24 +1065,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>normalize_contract_profile</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>normalize_contract_search_row</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>mcp_server/contract_analytics.py</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Shapes a Gold row into the get_contract_profile schema</t>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Shapes a Gold row into the search_contracts result schema</t>
         </is>
       </c>
     </row>
@@ -1033,24 +1092,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>ContractRepository</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>mcp_server/contract_repository.py</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Abstract swappable data boundary (list_all get_by_id search get_by_vendor)</t>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>normalize_contract_profile</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_analytics.py</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Shapes a Gold row into the get_contract_profile schema</t>
         </is>
       </c>
     </row>
@@ -1060,24 +1119,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>FabricContractRepository</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>mcp_server/contract_repository.py</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Fabric SQL Gold implementation of ContractRepository (works with offline interceptor)</t>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>parse_iso_date</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_analytics.py</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Parses ISO/datetime strings into date-only values for window filters</t>
         </is>
       </c>
     </row>
@@ -1087,24 +1146,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>get_contract_repository</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>mcp_server/contract_repository.py</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Returns the process-wide repository singleton used by MCP tools</t>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>resolve_renewal_window</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_analytics.py</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Resolves days_ahead or explicit ISO bounds into an inclusive renewal window</t>
         </is>
       </c>
     </row>
@@ -1114,24 +1173,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>find_overlapping_contracts</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>mcp_server/contract_risk.py</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Overlap detection over effective/expiration windows for same-vendor contracts</t>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>renewal_action_date</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_analytics.py</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Prefers RenewalDate and falls back to ExpirationDate as the renewal action date</t>
         </is>
       </c>
     </row>
@@ -1141,24 +1200,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>explain_contract_risks</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>mcp_server/contract_risk.py</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Computes known_facts and computed_risks for risk explanations</t>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>filter_renewals_in_window</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_analytics.py</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Keeps contracts whose RenewalActionDate falls inside [start, end] inclusive</t>
         </is>
       </c>
     </row>
@@ -1168,24 +1227,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>get_connection</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>mcp_server/fabric_sql.py</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Opens ODBC Driver 18 connection to Fabric with ActiveDirectoryDefault auth</t>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>list_contract_renewals</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_analytics.py</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Builds the renewals-list payload for a particular calendar window</t>
         </is>
       </c>
     </row>
@@ -1195,24 +1254,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>execute_query</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>mcp_server/fabric_sql.py</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Runs parameterized Fabric SQL and returns rows/columns</t>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>ContractRepository</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_repository.py</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Abstract swappable data boundary (list_all get_by_id search get_by_vendor)</t>
         </is>
       </c>
     </row>
@@ -1222,24 +1281,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>hybrid_semantic_search</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>mcp_server/azure_search.py</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Azure AI Search hybrid + semantic query used by search_cloud_blob_contracts</t>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>FabricContractRepository</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_repository.py</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Fabric SQL Gold implementation of ContractRepository (works with offline interceptor)</t>
         </is>
       </c>
     </row>
@@ -1249,1730 +1308,2829 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>config.get / config.require</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>mcp_server/config.py</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Loads optional/required env vars from the repo-root .env only</t>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>get_contract_repository</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_repository.py</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Returns the process-wide repository singleton used by MCP tools</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Fixtures</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>load_raw_contracts</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>mcp_server/linksquares_fixtures.py</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Loads LinSquare_Contracts_100_Updated_30bb.json raw contract records</t>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>find_overlapping_contracts</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_risk.py</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Overlap detection over effective/expiration windows for same-vendor contracts</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Fixtures</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>load_agreement_metadata</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>mcp_server/linksquares_fixtures.py</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Loads agreement_9a06.json metadata for fixture projection</t>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>explain_contract_risks</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_risk.py</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Computes known_facts and computed_risks for risk explanations</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Fixtures</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>project_contract_row</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>mcp_server/linksquares_fixtures.py</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Maps one LinkSquares raw contract into a Gold_Vendor_Contracts-shaped row</t>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>get_connection</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/fabric_sql.py</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Opens ODBC Driver 18 connection to Fabric with ActiveDirectoryDefault auth</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Fixtures</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>build_spend_rows</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>mcp_server/linksquares_fixtures.py</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Builds Gold_Vendor_Spend rollup rows from projected contracts</t>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>execute_query</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/fabric_sql.py</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Runs parameterized Fabric SQL and returns rows/columns</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Fixtures</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>build_search_documents</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>mcp_server/linksquares_fixtures.py</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Builds Azure_Search_Documents-shaped offline docs from projected contracts</t>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>hybrid_semantic_search</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/azure_search.py</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Azure AI Search hybrid + semantic query used by search_cloud_blob_contracts</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>config.get / config.require</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/config.py</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Loads optional/required env vars from the repo-root .env only</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
           <t>Fixtures</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>load_raw_contracts</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/linksquares_fixtures.py</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Loads LinSquare_Contracts_100_Updated_30bb.json raw contract records</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Fixtures</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>load_agreement_metadata</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/linksquares_fixtures.py</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Loads agreement_9a06.json metadata for fixture projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Fixtures</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>project_contract_row</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/linksquares_fixtures.py</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Maps one LinkSquares raw contract into a Gold_Vendor_Contracts-shaped row</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Fixtures</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>build_spend_rows</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/linksquares_fixtures.py</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Builds Gold_Vendor_Spend rollup rows from projected contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Fixtures</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>build_search_documents</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/linksquares_fixtures.py</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Builds Azure_Search_Documents-shaped offline docs from projected contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Fixtures</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
         <is>
           <t>build_offline_fixture_tables</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C42" s="3" t="inlineStr">
         <is>
           <t>mcp_server/linksquares_fixtures.py</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
         <is>
           <t>Assembles full offline tables (contracts spend search docs) for the interceptor</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B43" s="3" t="inlineStr">
         <is>
           <t>app.py (Flask)</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C43" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/app.py</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D43" s="3" t="inlineStr">
         <is>
           <t>Entry point</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E43" s="3" t="inlineStr">
         <is>
           <t>Starts Flask cognitive routing agent on COPILOT_HOST:COPILOT_PORT (default 0.0.0.0:3978)</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>POST /api/messages</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/app.py</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D44" s="3" t="inlineStr">
         <is>
           <t>API Route</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>Bot Framework ingress that runs agent turns and may persist persona memory</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>GET /health</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/app.py</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>API Route</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Liveness probe returning service ok status</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>run_turn</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/agent.py</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>One cognitive turn via LangChain or forced offline router; sanitizes default-compare hallucinations</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>get_agent_executor</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C47" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/agent.py</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
         <is>
           <t>Builds LangChain OpenAI-tools AgentExecutor bound to MCP tools and SYSTEM_PROMPT</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>SYSTEM_PROMPT</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/agent.py</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>Constant</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>System prompt encoding lifecycle procedures invoice OOS compare hard-stop and recommendation framework</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>System prompt encoding lifecycle procedures invoice OOS compare hard-stop renewal window list and recommendation framework</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>RENEWAL WINDOW LIST procedure</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>copilot_agent/agent.py</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>SYSTEM_PROMPT procedure for renewals list in a particular window via get_contract_renewals</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>PROACTIVE RENEWAL STRATEGY SHEETS</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>copilot_agent/agent.py</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>SYSTEM_PROMPT procedure recommending auto-renew / renegotiate / terminate from renewals or expiring tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>run_offline_turn</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C51" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/offline_router.py</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
         <is>
           <t>Deterministic intent-to-tool router when Azure OpenAI is bypassed or compare/memory intents need hard guarantees</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B52" s="3" t="inlineStr">
         <is>
           <t>is_invoice_out_of_scope</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C52" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/offline_router.py</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
         <is>
           <t>Hard-matches invoice/actual-spend intents and refuses them without tool calls</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B53" s="3" t="inlineStr">
         <is>
           <t>compare_unavailable_message</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C53" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/offline_router.py</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
         <is>
           <t>Exact hard-stop copy when compare sides cannot be resolved</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B54" s="3" t="inlineStr">
         <is>
           <t>sanitize_default_compare_hallucination</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C54" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/offline_router.py</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
         <is>
           <t>Strips legacy CON-0001/CON-0002 default-compare hallucinations down to the hard-stop message</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B55" s="3" t="inlineStr">
         <is>
           <t>_choose_tools</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/offline_router.py</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Maps user text to MCP tool names or persona_memory_recall</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Maps user text to MCP tool names including get_contract_renewals or persona_memory_recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>_parse_renewal_window_kwargs</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>copilot_agent/offline_router.py</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Parses next N days/months or ISO date ranges from renewal/expiry user text</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
         <is>
           <t>_build_compare_kwargs_from_text</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C57" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/offline_router.py</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
         <is>
           <t>Parses N-way compare targets suppliers and limits from user text</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>_build_compare_recommendation</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/offline_router.py</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
         <is>
           <t>Builds comparative recommendation sections only after a successful compare</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B59" s="3" t="inlineStr">
         <is>
           <t>_lifecycle_red_flag_audit</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C59" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/offline_router.py</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
         <is>
           <t>Offline red-flag compliance audit narrative from tool outputs</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>_lifecycle_financial_exposure</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C60" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/offline_router.py</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
         <is>
           <t>Offline financial exposure projection narrative from tool outputs</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B61" s="3" t="inlineStr">
         <is>
           <t>_lifecycle_renewal_strategy</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C61" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/offline_router.py</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Offline proactive renewal strategy narrative from tool outputs</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Offline proactive renewal strategy narrative from renewals/expiring tool outputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B62" s="3" t="inlineStr">
         <is>
           <t>_summarize_persona_memory</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C62" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/offline_router.py</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
         <is>
           <t>Serves previous/saved search recall from SQLite without MCP tools</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B63" s="3" t="inlineStr">
         <is>
           <t>DualMCPBridge</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C63" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/mcp_clients.py</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D63" s="3" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E63" s="3" t="inlineStr">
         <is>
           <t>Dual stdio MCP bridge to local mcp_server and optional uvx pgvector</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>DualMCPBridge.start / get_tools</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/mcp_clients.py</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
         <is>
           <t>Starts MCP clients and exposes LangChain tools to the cognitive agent</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B65" s="3" t="inlineStr">
         <is>
           <t>config.get / config.require</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C65" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/config.py</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
         <is>
           <t>Loads env vars from repo-root .env for the cognitive agent</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>Persona Memory</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B66" s="3" t="inlineStr">
         <is>
           <t>GET /api/memory/searches</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C66" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/app.py</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D66" s="3" t="inlineStr">
         <is>
           <t>API Route</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E66" s="3" t="inlineStr">
         <is>
           <t>Lists prior/saved searches for a persona with optional q and saved_only filters</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
         <is>
           <t>Persona Memory</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>POST /api/memory/searches</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/app.py</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>API Route</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>Explicitly pins/saves a search query for a persona</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
         <is>
           <t>Persona Memory</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B68" s="3" t="inlineStr">
         <is>
           <t>DELETE /api/memory/searches/&lt;id&gt;</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C68" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/app.py</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>API Route</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E68" s="3" t="inlineStr">
         <is>
           <t>Deletes one saved or auto-captured search by id</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
         <is>
           <t>Persona Memory</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>GET /api/memory/recall</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/app.py</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>API Route</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E69" s="3" t="inlineStr">
         <is>
           <t>Retrieves prior searches for chat recall phrases</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
         <is>
           <t>Persona Memory</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B70" s="3" t="inlineStr">
         <is>
           <t>GET /api/memory/conversations</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C70" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/app.py</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>API Route</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E70" s="3" t="inlineStr">
         <is>
           <t>Lists prior conversations for a persona</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>Persona Memory</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>DELETE /api/memory/conversations/&lt;id&gt;</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>copilot_agent/app.py</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>API Route</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Deletes one prior conversation (messages + linked searches) for a persona</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>DELETE /api/memory/conversations</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>copilot_agent/app.py</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>API Route</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Deletes all prior conversations for a persona</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>PersonaMemoryStore</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>memory/store.py</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>Class</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E73" s="3" t="inlineStr">
         <is>
           <t>SQLite store for personas conversations messages and searches</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
         <is>
           <t>Persona Memory</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B74" s="3" t="inlineStr">
         <is>
           <t>ensure_persona</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C74" s="3" t="inlineStr">
         <is>
           <t>memory/store.py</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
         <is>
           <t>Creates or updates a persona row used as the memory tenant key</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>Persona Memory</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B75" s="3" t="inlineStr">
         <is>
           <t>ensure_conversation / list_conversations</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C75" s="3" t="inlineStr">
         <is>
           <t>memory/store.py</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
         <is>
           <t>CRUD helpers for persona-scoped chat conversations</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
         <is>
           <t>Persona Memory</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B76" s="3" t="inlineStr">
         <is>
           <t>append_message / get_messages</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C76" s="3" t="inlineStr">
         <is>
           <t>memory/store.py</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
         <is>
           <t>Persists turns and loads chat history for agent/UI replay</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>Persona Memory</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B77" s="3" t="inlineStr">
         <is>
           <t>save_search</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C77" s="3" t="inlineStr">
         <is>
           <t>memory/store.py</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
         <is>
           <t>Auto-saves search-like queries or explicitly pins a search</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>Persona Memory</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B78" s="3" t="inlineStr">
         <is>
           <t>list_searches / delete_search</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C78" s="3" t="inlineStr">
         <is>
           <t>memory/store.py</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
         <is>
           <t>Lists filters and deletes saved/auto-captured searches</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>Persona Memory</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>delete_conversation</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>memory/store.py</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>Removes a conversation and cascading messages/searches; optional persona ownership check</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>delete_all_conversations</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>memory/store.py</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>Deletes every conversation for a persona and returns the count removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C81" s="3" t="inlineStr">
         <is>
           <t>memory/store.py</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
         <is>
           <t>Returns prior searches for retrieve-previous-searches flows</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
         <is>
           <t>Persona Memory</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B82" s="3" t="inlineStr">
         <is>
           <t>is_search_like</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C82" s="3" t="inlineStr">
         <is>
           <t>memory/store.py</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
         <is>
           <t>Detects whether user text looks like a searchable query for auto-save</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>Persona Memory</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B83" s="3" t="inlineStr">
         <is>
           <t>get_memory_store</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C83" s="3" t="inlineStr">
         <is>
           <t>memory/store.py</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
         <is>
           <t>Singleton accessor; DB path from VAL_MEMORY_DB or data/persona_memory.sqlite</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="7" t="inlineStr">
         <is>
           <t>Validation UI</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>app.py (Streamlit)</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>test_ui/app.py</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>Entry point</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E84" s="3" t="inlineStr">
         <is>
           <t>Streamlit validation chat UI posting Bot Framework activities to Flask</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t>Validation UI</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B85" s="3" t="inlineStr">
         <is>
           <t>_build_activity / _post_message</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C85" s="3" t="inlineStr">
         <is>
           <t>test_ui/app.py</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>Builds Bot Framework activities and POSTs them to /api/messages</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>Validation UI</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B86" s="3" t="inlineStr">
         <is>
           <t>_render_sidebar</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C86" s="3" t="inlineStr">
         <is>
           <t>test_ui/app.py</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>Sidebar for personas conversations and Saved searches (filter pin re-run delete)</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Sidebar for personas conversations Saved searches and delete prior chats</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="7" t="inlineStr">
         <is>
           <t>Validation UI</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>_delete_conversation</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>test_ui/app.py</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>Deletes a saved chat from persona memory and starts fresh if it was active</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>Validation UI</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
         <is>
           <t>_persist_turn / _switch_conversation</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C88" s="3" t="inlineStr">
         <is>
           <t>test_ui/app.py</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>Client-owned persona memory persistence and conversation switching</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>Validation UI</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B89" s="3" t="inlineStr">
         <is>
           <t>mock_messages_server.py</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C89" s="3" t="inlineStr">
         <is>
           <t>test_ui/mock_messages_server.py</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D89" s="3" t="inlineStr">
         <is>
           <t>Entry point</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E89" s="3" t="inlineStr">
         <is>
           <t>Local echo /api/messages backend for UI testing without the real agent</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
         <is>
           <t>Validation UI</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B90" s="3" t="inlineStr">
         <is>
           <t>config.get</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C90" s="3" t="inlineStr">
         <is>
           <t>test_ui/config.py</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
         <is>
           <t>Loads COPILOT_MESSAGES_URL and related env from repo-root .env</t>
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="8" t="inlineStr">
         <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B91" s="3" t="inlineStr">
         <is>
           <t>test_offline_mocks.py</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C91" s="3" t="inlineStr">
         <is>
           <t>mcp_server/test_offline_mocks.py</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D91" s="3" t="inlineStr">
         <is>
           <t>Test Entry</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
-        <is>
-          <t>Offline interceptor roundtrip; asserts tool bodies have no mock branches</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>Offline interceptor roundtrip including renewals window; asserts tool bodies have no mock branches</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="8" t="inlineStr">
         <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B92" s="3" t="inlineStr">
         <is>
           <t>test_poc_guards.py</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C92" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/test_poc_guards.py</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D92" s="3" t="inlineStr">
         <is>
           <t>Test Entry</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>POC guards for invoice OOS N-way compare hard-stop overlaps risk repository persona recall</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>POC guards for invoice OOS N-way compare hard-stop renewals window overlaps risk repository persona recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
         <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>test_contract_renewals_window_procedure</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>copilot_agent/test_poc_guards.py</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>Asserts get_contract_renewals days_ahead and ISO window filtering including supplier filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="8" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>test_offline_router_renewal_window_routing</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>copilot_agent/test_poc_guards.py</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Asserts renewals-list intents route to get_contract_renewals and window kwargs parse correctly</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>test_invoice_guardrail_hard_match</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/test_poc_guards.py</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E95" s="3" t="inlineStr">
         <is>
           <t>Asserts invoice/actual-spend intents are refused without tool calls</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="8" t="inlineStr">
         <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B96" s="3" t="inlineStr">
         <is>
           <t>test_compare_contracts_any_ids_and_nway</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/test_poc_guards.py</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D96" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>Asserts any-ID and N-way compare_contracts behavior</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="8" t="inlineStr">
         <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B97" s="3" t="inlineStr">
         <is>
           <t>test_offline_router_missing_contract_no_default_compare</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C97" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/test_poc_guards.py</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D97" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E97" s="3" t="inlineStr">
         <is>
           <t>Asserts missing compare hard-stops with no CON-0001 default table or recommendation</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="8" t="inlineStr">
         <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>test_sanitize_default_compare_hallucination</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/test_poc_guards.py</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E98" s="3" t="inlineStr">
         <is>
           <t>Asserts legacy default-compare hallucination text is sanitized</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="8" t="inlineStr">
         <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>test_persona_memory_recall_routing</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>copilot_agent/test_poc_guards.py</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E99" s="3" t="inlineStr">
         <is>
           <t>Asserts previous-search recall phrases route through offline persona memory</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>test_store.py</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>memory/test_store.py</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>Test Entry</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
-          <t>Unit tests for persona memory CRUD pin/filter/delete and search-like detection</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>Unit tests for persona memory CRUD pin/filter/delete conversations and search-like detection</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8" t="inlineStr">
         <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>test_delete_conversation_and_all</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>memory/test_store.py</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>Asserts persona-scoped conversation delete and delete-all cascade messages/searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="8" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>test_bot_schema.py</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>test_ui/test_bot_schema.py</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>Test Entry</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E102" s="3" t="inlineStr">
         <is>
           <t>Bot Framework mock activity schema smoke test</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="8" t="inlineStr">
         <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B103" s="3" t="inlineStr">
         <is>
           <t>test_streamlit_ui.py</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C103" s="3" t="inlineStr">
         <is>
           <t>test_ui/test_streamlit_ui.py</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D103" s="3" t="inlineStr">
         <is>
           <t>Test Entry</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E103" s="3" t="inlineStr">
         <is>
           <t>Streamlit AppTest chat roundtrip against mock /api/messages</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="9" t="inlineStr">
         <is>
           <t>Generators</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B104" s="3" t="inlineStr">
         <is>
           <t>generate_architecture_diagram.py</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C104" s="3" t="inlineStr">
         <is>
           <t>docs/generate_architecture_diagram.py</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D104" s="3" t="inlineStr">
         <is>
           <t>Entry point</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E104" s="3" t="inlineStr">
         <is>
           <t>ReportLab generator for VAL_CoPilot_Architecture_and_Process_Flow.pdf</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="9" t="inlineStr">
         <is>
           <t>Generators</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B105" s="3" t="inlineStr">
         <is>
           <t>generate_architecture_pptx.py</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C105" s="3" t="inlineStr">
         <is>
           <t>docs/generate_architecture_pptx.py</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D105" s="3" t="inlineStr">
         <is>
           <t>Entry point</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E105" s="3" t="inlineStr">
         <is>
           <t>PowerPoint generator for architecture/process-flow deck</t>
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+  </sheetData>
+  <autoFilter ref="A1:E105"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>Script_File</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>Procedure_Count</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>Contains_Types</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>Example_Procedures</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>Primary_Use</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>copilot_agent/agent.py</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Constant, Function</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>run_turn; get_agent_executor; SYSTEM_PROMPT; RENEWAL WINDOW LIST procedure; PROACTIVE RENEWAL STRATEGY SHEETS</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>run_turn</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>copilot_agent/app.py</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>API Route, Entry point</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>app.py (Flask); POST /api/messages; GET /health; GET /api/memory/searches; POST /api/memory/searches…</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Starts Flask cognitive routing agent on COPILOT_HOST:COPILOT_PORT (default 0.0.0.0:3978)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>copilot_agent/config.py</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>config.get / config.require</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>config.get / config.require</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>copilot_agent/mcp_clients.py</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Class, Function</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>DualMCPBridge; DualMCPBridge.start / get_tools</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>DualMCPBridge</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>copilot_agent/offline_router.py</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>run_offline_turn; is_invoice_out_of_scope; compare_unavailable_message; sanitize_default_compare_hallucination; _choose_tools…</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>run_offline_turn</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Fixtures</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/linksquares_fixtures.py</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>load_raw_contracts; load_agreement_metadata; project_contract_row; build_spend_rows; build_search_documents…</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>load_raw_contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Generators</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>docs/generate_architecture_diagram.py</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Entry point</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>generate_architecture_diagram.py</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>ReportLab generator for VAL_CoPilot_Architecture_and_Process_Flow.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Generators</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>docs/generate_architecture_pptx.py</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Entry point</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>generate_architecture_pptx.py</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>PowerPoint generator for architecture/process-flow deck</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/azure_search.py</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>hybrid_semantic_search</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>hybrid_semantic_search</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/config.py</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>config.get / config.require</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>config.get / config.require</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_analytics.py</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>build_criteria; filter_contracts; resolve_contract; compare_contract_rows; compare_many_contract_rows…</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>build_criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_repository.py</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Class, Function</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>ContractRepository; FabricContractRepository; get_contract_repository</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>ContractRepository</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_risk.py</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>find_overlapping_contracts; explain_contract_risks</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>find_overlapping_contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/fabric_sql.py</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>get_connection; execute_query</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>get_connection</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/server.py</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Entry point, Function, MCP Tool</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>server.py (mcp.run); get_expiring_contracts; get_contract_renewals; get_vendor_spend_summary; compare_contracts…</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>FastMCP stdio server; installs LinkSquares offline interceptor when USE_OFFLINE_MOCKS is set and registers all MCP tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Persona Memory</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>DELETE /api/memory/conversations/&lt;id&gt;</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>copilot_agent/app.py</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>API Route</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>Deletes one prior conversation (messages + linked searches) for a persona</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>Persona Memory</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>DELETE /api/memory/conversations</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>copilot_agent/app.py</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>API Route</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>Deletes all prior conversations for a persona</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>Persona Memory</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>delete_conversation</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>memory/store.py</t>
         </is>
       </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>Removes a conversation and cascading messages/searches; optional persona ownership check</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>Persona Memory</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>delete_all_conversations</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>memory/store.py</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>Deletes every conversation for a persona and returns the count removed</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="C17" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Class, Function</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>PersonaMemoryStore; ensure_persona; ensure_conversation / list_conversations; append_message / get_messages; save_search…</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>PersonaMemoryStore</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>copilot_agent/test_poc_guards.py</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Test, Test Entry</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>test_poc_guards.py; test_contract_renewals_window_procedure; test_offline_router_renewal_window_routing; test_invoice_guardrail_hard_match; test_compare_contracts_any_ids_and_nway…</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>POC guards for invoice OOS N-way compare hard-stop renewals window overlaps risk repository persona recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>mcp_server/test_offline_mocks.py</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Test Entry</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>test_offline_mocks.py</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Offline interceptor roundtrip including renewals window; asserts tool bodies have no mock branches</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>memory/test_store.py</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Test, Test Entry</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>test_store.py; test_delete_conversation_and_all</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Unit tests for persona memory CRUD pin/filter/delete conversations and search-like detection</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>test_ui/test_bot_schema.py</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Test Entry</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>test_bot_schema.py</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Bot Framework mock activity schema smoke test</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>test_ui/test_streamlit_ui.py</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Test Entry</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>test_streamlit_ui.py</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Streamlit AppTest chat roundtrip against mock /api/messages</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>Validation UI</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>_delete_conversation</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>test_ui/app.py</t>
         </is>
       </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>Streamlit helper to delete a saved chat from persona memory and start fresh if it was active</t>
+      <c r="C23" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Entry point, Function</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>app.py (Streamlit); _build_activity / _post_message; _render_sidebar; _delete_conversation; _persist_turn / _switch_conversation</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Streamlit validation chat UI posting Bot Framework activities to Flask</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Validation UI</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>test_ui/config.py</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>config.get</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>config.get</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Validation UI</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>test_ui/mock_messages_server.py</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Entry point</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>mock_messages_server.py</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Local echo /api/messages backend for UI testing without the real agent</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E93"/>
+  <autoFilter ref="A1:F25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/VAL_CoPilot_Python_Procedures_Catalog.xlsx
+++ b/docs/VAL_CoPilot_Python_Procedures_Catalog.xlsx
@@ -12,9 +12,7 @@
     <sheet name="Scripts Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Procedures Catalog'!$A$1:$E$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Diagram Gap Analysis'!$A$1:$D$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scripts Summary'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Procedures Catalog'!$A$1:$E$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,17 +30,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -51,42 +43,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000B1F33"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D1FAE5"/>
+        <fgColor rgb="00C65911"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FEF3C7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9F3F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00EDE9FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F1F5F9"/>
+        <fgColor rgb="00548235"/>
       </patternFill>
     </fill>
   </fills>
@@ -100,52 +67,34 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </left>
       <right style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </right>
       <top style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00CBD5E1"/>
+        <color rgb="00D9D9D9"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -511,14 +460,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="72" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -554,22 +503,22 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>server.py (mcp.run)</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Entry point</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>FastMCP stdio server; installs LinkSquares offline interceptor when USE_OFFLINE_MOCKS is set and registers all MCP tools</t>
         </is>
@@ -581,22 +530,22 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>search_contracts</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Structured Gold metadata search; returns contract_not_present when nothing matches</t>
         </is>
@@ -608,22 +557,22 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>get_contract_profile</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Full normalized profile for one ContractID; not-present if missing</t>
         </is>
@@ -635,24 +584,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>compare_contracts</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Pairwise or N-way compare of any contract IDs; hard-stops if unresolved</t>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Pairwise or N-way compare of any contract IDs; hard-stops with exact unavailable message if sides cannot be resolved</t>
         </is>
       </c>
     </row>
@@ -662,24 +611,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>list_renewals_in_window</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>Diagram tool — Renewal Window List for days_ahead or window_start/window_end</t>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Diagram tool — Renewal Window List for days_ahead or inclusive window_start/window_end</t>
         </is>
       </c>
     </row>
@@ -689,22 +638,22 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>get_contract_renewals</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Alias for list_renewals_in_window (backward compatible)</t>
         </is>
@@ -716,22 +665,22 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>find_overlaps</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Detects same-vendor effective-to-expiration date overlaps</t>
         </is>
@@ -743,22 +692,22 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>identify_missing_fields</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Diagram tool — Missing Data Checker for incomplete commercial fields</t>
         </is>
@@ -770,22 +719,22 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>check_missing_contract_fields</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Alias for identify_missing_fields (backward compatible)</t>
         </is>
@@ -797,22 +746,22 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>explain_contract_risk</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Returns known_facts versus computed_risks for filtered contracts</t>
         </is>
@@ -824,24 +773,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>get_expiring_contracts</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Returns contracts approaching expiration within a days_ahead lookahead</t>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Returns contracts approaching expiration within a days_ahead lookahead window</t>
         </is>
       </c>
     </row>
@@ -851,22 +800,22 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>get_vendor_spend_summary</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Rolls up committed contract value by supplier (not invoice spend)</t>
         </is>
@@ -878,24 +827,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>search_cloud_blob_contracts</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>Hybrid semantic / clause search via Azure AI Search (or offline docs)</t>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid semantic / clause search via Azure AI Search (or offline search docs)</t>
         </is>
       </c>
     </row>
@@ -905,22 +854,22 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>fabric_health_check</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>MCP Tool</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Probes Fabric SQL connectivity or offline interceptor health</t>
         </is>
@@ -932,24 +881,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>list_contract_renewals</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>mcp_server/contract_analytics.py</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>Builds renewals-list payload for a particular calendar window</t>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>_install_offline_mock_interceptor</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/server.py</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Patches pyodbc/pandas/Azure Search so production-shaped tools hit LinkSquares fixtures</t>
         </is>
       </c>
     </row>
@@ -959,24 +908,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>filter_renewals_in_window</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>build_criteria</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>mcp_server/contract_analytics.py</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>Keeps contracts whose RenewalActionDate falls inside [start, end]</t>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Builds filter criteria (supplier type id name cost) for resolve/filter paths</t>
         </is>
       </c>
     </row>
@@ -986,24 +935,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>resolve_renewal_window</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>filter_contracts</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>mcp_server/contract_analytics.py</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Resolves days_ahead or explicit ISO bounds into an inclusive window</t>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Filters in-memory contract rows against active criteria</t>
         </is>
       </c>
     </row>
@@ -1013,24 +962,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>renewal_action_date</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>resolve_contract</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>mcp_server/contract_analytics.py</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>Prefers RenewalDate; falls back to ExpirationDate</t>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Resolves a single best-matching contract for profile/compare sides</t>
         </is>
       </c>
     </row>
@@ -1040,24 +989,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>check_missing_fields_in_rows</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>compare_contract_rows</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>mcp_server/contract_analytics.py</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Computes missing required commercial fields per row</t>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Pairwise field-diff comparison between two resolved contracts</t>
         </is>
       </c>
     </row>
@@ -1067,24 +1016,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>compare_contract_rows / compare_many_contract_rows</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>compare_many_contract_rows</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>mcp_server/contract_analytics.py</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>Pairwise and N-way field comparison engines</t>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>N-way field matrix comparison across any number of resolved contracts</t>
         </is>
       </c>
     </row>
@@ -1094,24 +1043,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>ContractRepository / FabricContractRepository</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>mcp_server/contract_repository.py</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Swappable Gold/offline contract data boundary</t>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>check_missing_fields_in_rows</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_analytics.py</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Computes which required commercial fields are missing on each row</t>
         </is>
       </c>
     </row>
@@ -1121,24 +1070,24 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>find_overlapping_contracts</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>mcp_server/contract_risk.py</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>Overlap Detection Engine over same-vendor date windows</t>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>normalize_contract_search_row</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_analytics.py</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Shapes a Gold row into the search_contracts result schema</t>
         </is>
       </c>
     </row>
@@ -1148,515 +1097,2378 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>normalize_contract_profile</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_analytics.py</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Shapes a Gold row into the get_contract_profile schema</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>parse_iso_date</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_analytics.py</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Parses ISO/datetime strings into date-only values for window filters</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>resolve_renewal_window</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_analytics.py</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Resolves days_ahead or explicit ISO bounds into an inclusive renewal window</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>renewal_action_date</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_analytics.py</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Prefers RenewalDate and falls back to ExpirationDate as the renewal action date</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>filter_renewals_in_window</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_analytics.py</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Keeps contracts whose RenewalActionDate falls inside [start, end] inclusive</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>list_contract_renewals</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_analytics.py</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Builds the renewals-list payload for a particular calendar window</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ContractRepository</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_repository.py</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Abstract swappable data boundary (list_all get_by_id search get_by_vendor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>FabricContractRepository</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_repository.py</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Fabric SQL Gold implementation of ContractRepository (works with offline interceptor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>get_contract_repository</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_repository.py</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Returns the process-wide repository singleton used by MCP tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>find_overlapping_contracts</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_risk.py</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Overlap detection over effective/expiration windows for same-vendor contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>explain_contract_risks</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>mcp_server/contract_risk.py</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Renewal/Risk engine helper separating known_facts from computed_risks</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Computes known_facts and computed_risks for risk explanations</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>get_connection</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/fabric_sql.py</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Opens ODBC Driver 18 connection to Fabric with ActiveDirectoryDefault auth</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>execute_query</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/fabric_sql.py</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Runs parameterized Fabric SQL and returns rows/columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>hybrid_semantic_search</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/azure_search.py</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Azure AI Search hybrid + semantic query used by search_cloud_blob_contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>config.get / config.require</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/config.py</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Loads optional/required env vars from the repo-root .env only</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Fixtures</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>load_raw_contracts</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/linksquares_fixtures.py</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Loads LinSquare_Contracts_100_Updated_30bb.json raw contract records</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Fixtures</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>load_agreement_metadata</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/linksquares_fixtures.py</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Loads agreement_9a06.json metadata for fixture projection</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Fixtures</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>project_contract_row</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/linksquares_fixtures.py</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Maps one LinkSquares raw contract into a Gold_Vendor_Contracts-shaped row</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Fixtures</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>build_spend_rows</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/linksquares_fixtures.py</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Builds Gold_Vendor_Spend rollup rows from projected contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Fixtures</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>build_search_documents</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/linksquares_fixtures.py</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Builds Azure_Search_Documents-shaped offline docs from projected contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Fixtures</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>build_offline_fixture_tables</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
         <is>
           <t>mcp_server/linksquares_fixtures.py</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>Projects LinkSquares JSON into Gold-shaped offline tables</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Assembles full offline tables (contracts spend search docs) for the interceptor</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>app.py (Flask)</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
         <is>
           <t>copilot_agent/app.py</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Entry point</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Flask cognitive routing agent with /api/messages and memory APIs</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Starts Flask cognitive routing agent on COPILOT_HOST:COPILOT_PORT (default 0.0.0.0:3978)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/messages</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/app.py</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>API Route</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Bot Framework ingress that runs agent turns and may persist persona memory</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>GET /health</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/app.py</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>API Route</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Liveness probe returning service ok status</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>run_turn</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
         <is>
           <t>copilot_agent/agent.py</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>LangChain or offline cognitive turn with SYSTEM_PROMPT lifecycle procedures</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>One cognitive turn via LangChain or forced offline router; sanitizes default-compare hallucinations</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>get_agent_executor</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/agent.py</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Builds LangChain OpenAI-tools AgentExecutor bound to MCP tools and SYSTEM_PROMPT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>SYSTEM_PROMPT diagram tools</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>copilot_agent/agent.py</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Constant</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Routes to search/profile/compare/list_renewals_in_window/find_overlaps/identify_missing_fields/explain_contract_risk</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>System prompt encoding lifecycle procedures, invoice OOS, compare hard-stop, and diagram tools (search/profile/compare/list_renewals_in_window/find_overlaps/identify_missing_fields/explain_contract_risk)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>RENEWAL WINDOW LIST procedure</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>copilot_agent/agent.py</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Constant</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Lifecycle procedure for renewals list in a particular window</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>SYSTEM_PROMPT procedure for renewals list in a particular window via list_renewals_in_window (alias get_contract_renewals)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>run_offline_turn / _choose_tools</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>PROACTIVE RENEWAL STRATEGY SHEETS</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/agent.py</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Constant</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>SYSTEM_PROMPT procedure recommending auto-renew / renegotiate / terminate from renewals or expiring tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>run_offline_turn</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
         <is>
           <t>copilot_agent/offline_router.py</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E30" s="3" t="inlineStr">
-        <is>
-          <t>Deterministic intent→tool router including diagram-aligned tool names</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Deterministic intent-to-tool router when Azure OpenAI is bypassed; uses diagram-aligned tool names</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>is_invoice_out_of_scope</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/offline_router.py</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Hard-matches invoice/actual-spend intents and refuses them without tool calls</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>compare_unavailable_message</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/offline_router.py</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Exact hard-stop copy when compare sides cannot be resolved</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>sanitize_default_compare_hallucination</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/offline_router.py</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Strips legacy CON-0001/CON-0002 default-compare hallucinations down to the hard-stop message</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>_choose_tools</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/offline_router.py</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Maps user text to MCP tool names including list_renewals_in_window, identify_missing_fields, or persona_memory_recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>_parse_renewal_window_kwargs</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
         <is>
           <t>copilot_agent/offline_router.py</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>Parses next N days/months or ISO ranges for list_renewals_in_window</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Parses next N days/months or ISO date ranges for list_renewals_in_window</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>_build_compare_kwargs_from_text</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/offline_router.py</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Parses N-way compare targets suppliers and limits from user text</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>_build_compare_recommendation</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/offline_router.py</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Builds comparative recommendation sections only after a successful compare</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>_lifecycle_red_flag_audit</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/offline_router.py</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Offline red-flag compliance audit narrative from tool outputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>_lifecycle_financial_exposure</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/offline_router.py</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Offline financial exposure projection narrative from tool outputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>_lifecycle_renewal_strategy</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
         <is>
           <t>copilot_agent/offline_router.py</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>Response formatter for Proactive Renewal Strategy Sheet</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Offline proactive renewal strategy narrative from renewals/expiring tool outputs</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>_lifecycle_red_flag_audit</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>_summarize_persona_memory</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
         <is>
           <t>copilot_agent/offline_router.py</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>Response formatter for Red-Flag Compliance Audit from missing fields</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Serves previous/saved search recall from SQLite without MCP tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>DualMCPBridge</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/mcp_clients.py</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Dual stdio MCP bridge to local mcp_server and optional uvx pgvector</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>DualMCPBridge.start / get_tools</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/mcp_clients.py</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Starts MCP clients and exposes LangChain tools to the cognitive agent</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>config.get / config.require</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/config.py</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Loads env vars from repo-root .env for the cognitive agent</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>Persona Memory</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/memory/searches</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/app.py</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>API Route</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Lists prior/saved searches for a persona with optional q and saved_only filters</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/memory/searches</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/app.py</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>API Route</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Explicitly pins/saves a search query for a persona</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>DELETE /api/memory/searches/&lt;id&gt;</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/app.py</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>API Route</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Deletes one saved or auto-captured search by id</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/memory/recall</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/app.py</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>API Route</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Retrieves prior searches for chat recall phrases</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/memory/conversations</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/app.py</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>API Route</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Lists prior conversations for a persona</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>DELETE /api/memory/conversations/&lt;id&gt;</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/app.py</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>API Route</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Deletes one prior conversation (messages + linked searches) for a persona</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>DELETE /api/memory/conversations</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="C74" s="2" t="inlineStr">
         <is>
           <t>copilot_agent/app.py</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>API Route</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>Deletes prior conversations for a persona (one or all)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Deletes all prior conversations for a persona</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>Persona Memory</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>delete_conversation / delete_all_conversations</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>PersonaMemoryStore</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
         <is>
           <t>memory/store.py</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>SQLite cascade delete for conversations messages and linked searches</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="inlineStr">
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>SQLite store for personas conversations messages and searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>ensure_persona</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>memory/store.py</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Creates or updates a persona row used as the memory tenant key</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>ensure_conversation / list_conversations</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>memory/store.py</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>CRUD helpers for persona-scoped chat conversations</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>append_message / get_messages</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>memory/store.py</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Persists turns and loads chat history for agent/UI replay</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>save_search</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>memory/store.py</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Auto-saves search-like queries or explicitly pins a search</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>list_searches / delete_search</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>memory/store.py</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Lists filters and deletes saved/auto-captured searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>delete_conversation</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>memory/store.py</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Removes a conversation and cascading messages/searches; optional persona ownership check</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>delete_all_conversations</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>memory/store.py</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Deletes every conversation for a persona and returns the count removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>memory/store.py</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Returns prior searches for retrieve-previous-searches flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>is_search_like</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>memory/store.py</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Detects whether user text looks like a searchable query for auto-save</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>get_memory_store</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>memory/store.py</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Singleton accessor; DB path from VAL_MEMORY_DB or data/persona_memory.sqlite</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Validation UI</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>app.py (Streamlit)</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>test_ui/app.py</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>Entry point</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Streamlit validation chat UI posting Bot Framework activities to Flask</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Validation UI</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>_build_activity / _post_message</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>test_ui/app.py</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Builds Bot Framework activities and POSTs them to /api/messages</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Validation UI</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>_render_sidebar</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>test_ui/app.py</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Sidebar for personas conversations Saved searches and delete prior chats</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Validation UI</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>_delete_conversation</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="C89" s="2" t="inlineStr">
         <is>
           <t>test_ui/app.py</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Streamlit delete prior chats from persona memory</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Deletes a saved chat from persona memory and starts fresh if it was active</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Validation UI</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>_persist_turn / _switch_conversation</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>test_ui/app.py</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Client-owned persona memory persistence and conversation switching</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Validation UI</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>mock_messages_server.py</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>test_ui/mock_messages_server.py</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>Entry point</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Local echo /api/messages backend for UI testing without the real agent</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Validation UI</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>config.get</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>test_ui/config.py</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Loads COPILOT_MESSAGES_URL and related env from repo-root .env</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>test_offline_mocks.py</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/test_offline_mocks.py</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>Test Entry</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Offline interceptor roundtrip including renewals window; asserts tool bodies have no mock branches</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>test_poc_guards.py</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/test_poc_guards.py</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>Test Entry</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>POC guards for invoice OOS N-way compare hard-stop renewals window overlaps risk repository persona recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>test_contract_renewals_window_procedure</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="C95" s="2" t="inlineStr">
         <is>
           <t>copilot_agent/test_poc_guards.py</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>Asserts list_renewals_in_window window filtering and alias parity</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Asserts list_renewals_in_window window filtering and get_contract_renewals alias parity</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>test_offline_router_renewal_window_routing</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/test_poc_guards.py</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Asserts renewals-list intents route to list_renewals_in_window and window kwargs parse correctly</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>test_invoice_guardrail_hard_match</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/test_poc_guards.py</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Asserts invoice/actual-spend intents are refused without tool calls</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>test_compare_contracts_any_ids_and_nway</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/test_poc_guards.py</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Asserts any-ID and N-way compare_contracts behavior</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>test_offline_router_missing_contract_no_default_compare</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/test_poc_guards.py</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Asserts missing compare hard-stops with no CON-0001 default table or recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>test_sanitize_default_compare_hallucination</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/test_poc_guards.py</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Asserts legacy default-compare hallucination text is sanitized</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>test_persona_memory_recall_routing</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/test_poc_guards.py</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Asserts previous-search recall phrases route through offline persona memory</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>test_store.py</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>memory/test_store.py</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>Test Entry</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Unit tests for persona memory CRUD pin/filter/delete conversations and search-like detection</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>test_delete_conversation_and_all</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>memory/test_store.py</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>Test</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Asserts persona-scoped conversation delete and delete-all cascade messages/searches</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>test_bot_schema.py</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>test_ui/test_bot_schema.py</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>Test Entry</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Bot Framework mock activity schema smoke test</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>test_streamlit_ui.py</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>test_ui/test_streamlit_ui.py</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Test Entry</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Streamlit AppTest chat roundtrip against mock /api/messages</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Generators</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>generate_architecture_diagram.py</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>docs/generate_architecture_diagram.py</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Entry point</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>ReportLab generator for VAL_CoPilot_Architecture_and_Process_Flow.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Generators</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>generate_architecture_pptx.py</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>docs/generate_architecture_pptx.py</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>Entry point</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>PowerPoint generator for architecture/process-flow deck</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>test_identify_missing_fields_diagram_alias</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="C108" s="2" t="inlineStr">
         <is>
           <t>copilot_agent/test_poc_guards.py</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Asserts identify_missing_fields diagram tool and check_missing alias</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="8" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>test_offline_router_renewal_window_routing</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>test_offline_router_missing_fields_routing</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
         <is>
           <t>copilot_agent/test_poc_guards.py</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Test</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Asserts renewals-list intents route to list_renewals_in_window</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Asserts missing-field intents route to identify_missing_fields</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>append_response_time / strip_response_time</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/response_time.py</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Appends per-query Response time footer to replies; strips footers from chat history</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>test_offline_router_missing_fields_routing</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>copilot_agent/test_poc_guards.py</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Asserts missing-field intents route to identify_missing_fields</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>Generators</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>generate_architecture_diagram.py</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>docs/generate_architecture_diagram.py</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>Entry point</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>Architecture PDF generator</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="9" t="inlineStr">
-        <is>
-          <t>Generators</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>generate_architecture_pptx.py</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>docs/generate_architecture_pptx.py</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>Entry point</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>Architecture PPTX generator</t>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>test_response_time.py</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/test_response_time.py</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Test Entry</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Unit tests for response-time format/append/strip helpers</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E42"/>
+  <autoFilter ref="A1:E111"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1672,34 +3484,34 @@
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="70" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Diagram Tool</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Source Procedure</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>search_contracts</t>
         </is>
@@ -1709,19 +3521,19 @@
           <t>Present</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>search_contracts</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Already implemented</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>get_contract_profile</t>
         </is>
@@ -1731,19 +3543,19 @@
           <t>Present</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>get_contract_profile</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Already implemented</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>compare_contracts</t>
         </is>
@@ -1753,41 +3565,41 @@
           <t>Present</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>compare_contracts</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Already implemented</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>list_renewals_in_window</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>list_renewals_in_window (+ alias get_contract_renewals)</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Was get_contract_renewals; now diagram-aligned primary name</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>find_overlaps</t>
         </is>
@@ -1797,41 +3609,41 @@
           <t>Present</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>find_overlaps</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Already implemented</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>identify_missing_fields</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Added</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>identify_missing_fields (+ alias check_missing_contract_fields)</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Was check_missing_contract_fields; now diagram-aligned primary name</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>explain_contract_risk</t>
         </is>
@@ -1841,19 +3653,19 @@
           <t>Present</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>explain_contract_risk</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Already implemented</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>other tools</t>
         </is>
@@ -1863,19 +3675,18 @@
           <t>Present</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>get_expiring_contracts; get_vendor_spend_summary; search_cloud_blob_contracts; fabric_health_check</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Extra POC tools beyond the diagram ellipsis</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1886,316 +3697,265 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Script_File</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Procedure_Count</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Contains_Types</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
-        <is>
-          <t>Example_Procedures</t>
-        </is>
-      </c>
-      <c r="F1" s="10" t="inlineStr">
-        <is>
-          <t>Primary_Use</t>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Sample_Procedures</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>copilot_agent/agent.py</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Constant, Function</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>run_turn; get_agent_executor; SYSTEM_PROMPT diagram tools; RENEWAL WINDOW LIST procedure; PROACTIVE RENEWAL STRATEGY SHEETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/app.py</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Constant, Function</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>run_turn; SYSTEM_PROMPT diagram tools; RENEWAL WINDOW LIST procedure</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>run_turn</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>API Route, Entry point</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>app.py (Flask); POST /api/messages; GET /health</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>copilot_agent/app.py</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/config.py</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>config.get / config.require</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/mcp_clients.py</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>API Route, Entry point</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>app.py (Flask); DELETE /api/memory/conversations</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>Flask cognitive routing agent with /api/messages and memory APIs</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Class, Function</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>DualMCPBridge; DualMCPBridge.start / get_tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Cognitive Router</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>copilot_agent/offline_router.py</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>run_offline_turn / _choose_tools; _parse_renewal_window_kwargs; _lifecycle_renewal_strategy; _lifecycle_red_flag_audit</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>run_offline_turn / _choose_tools</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Fixtures</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>mcp_server/linksquares_fixtures.py</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
+      <c r="C6" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>run_offline_turn; is_invoice_out_of_scope; compare_unavailable_message; sanitize_default_compare_hallucination; _choose_tools; ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Cognitive Router</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/response_time.py</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>build_offline_fixture_tables</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>build_offline_fixture_tables</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Generators</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>docs/generate_architecture_diagram.py</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>Entry point</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>generate_architecture_diagram.py</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>Architecture PDF generator</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Generators</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>docs/generate_architecture_pptx.py</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t>Entry point</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>generate_architecture_pptx.py</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>Architecture PPTX generator</t>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>append_response_time / strip_response_time</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>MCP Tools</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>mcp_server/contract_analytics.py</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
+          <t>Fixtures</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/linksquares_fixtures.py</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>list_contract_renewals; filter_renewals_in_window; resolve_renewal_window; renewal_action_date; check_missing_fields_in_rows…</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>list_contract_renewals</t>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>load_raw_contracts; load_agreement_metadata; project_contract_row; build_spend_rows; build_search_documents; ...</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>MCP Tools</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>mcp_server/contract_repository.py</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
+          <t>Generators</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>docs/generate_architecture_diagram.py</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>ContractRepository / FabricContractRepository</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>ContractRepository / FabricContractRepository</t>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Entry point</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>generate_architecture_diagram.py</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>MCP Tools</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>mcp_server/contract_risk.py</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>find_overlapping_contracts; explain_contract_risks</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>find_overlapping_contracts</t>
+          <t>Generators</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>docs/generate_architecture_pptx.py</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Entry point</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>generate_architecture_pptx.py</t>
         </is>
       </c>
     </row>
@@ -2205,122 +3965,451 @@
           <t>MCP Tools</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/azure_search.py</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>hybrid_semantic_search</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/config.py</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>config.get / config.require</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_analytics.py</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>build_criteria; filter_contracts; resolve_contract; compare_contract_rows; compare_many_contract_rows; ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_repository.py</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Class, Function</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>ContractRepository; FabricContractRepository; get_contract_repository</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/contract_risk.py</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>find_overlapping_contracts; explain_contract_risks</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/fabric_sql.py</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>get_connection; execute_query</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>MCP Tools</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>mcp_server/server.py</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>Entry point, MCP Tool</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>server.py (mcp.run); search_contracts; get_contract_profile; compare_contracts; list_renewals_in_window…</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>FastMCP stdio server; installs LinkSquares offline interceptor when USE_OFFLINE_MOCKS is set and registers all MCP tools</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="C17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Entry point, Function, MCP Tool</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>server.py (mcp.run); search_contracts; get_contract_profile; compare_contracts; list_renewals_in_window; ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>Persona Memory</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/app.py</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>API Route</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/memory/searches; POST /api/memory/searches; DELETE /api/memory/searches/&lt;id&gt;; GET /api/memory/recall; GET /api/memory/conversations; ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Persona Memory</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>memory/store.py</t>
         </is>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C19" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Class, Function</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>PersonaMemoryStore; ensure_persona; ensure_conversation / list_conversations; append_message / get_messages; save_search; ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/test_poc_guards.py</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Test, Test Entry</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>test_poc_guards.py; test_contract_renewals_window_procedure; test_offline_router_renewal_window_routing; test_invoice_guardrail_hard_match; test_compare_contracts_any_ids_and_nway; ...</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>copilot_agent/test_response_time.py</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>delete_conversation / delete_all_conversations</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>delete_conversation / delete_all_conversations</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Test Entry</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>test_response_time.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>Tests</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>copilot_agent/test_poc_guards.py</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Test</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>test_contract_renewals_window_procedure; test_identify_missing_fields_diagram_alias; test_offline_router_renewal_window_routing; test_offline_router_missing_fields_routing</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>test_contract_renewals_window_procedure</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>mcp_server/test_offline_mocks.py</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Test Entry</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>test_offline_mocks.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>memory/test_store.py</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Test, Test Entry</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>test_store.py; test_delete_conversation_and_all</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>test_ui/test_bot_schema.py</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Test Entry</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>test_bot_schema.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Tests</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>test_ui/test_streamlit_ui.py</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Test Entry</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>test_streamlit_ui.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>Validation UI</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>test_ui/app.py</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C26" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Entry point, Function</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>app.py (Streamlit); _build_activity / _post_message; _render_sidebar; _delete_conversation; _persist_turn / _switch_conversation</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Validation UI</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>test_ui/config.py</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Function</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>_delete_conversation</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>_delete_conversation</t>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>config.get</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Validation UI</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>test_ui/mock_messages_server.py</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Entry point</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>mock_messages_server.py</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>